--- a/sampleprojects/Scopa/excel/Scopa.xlsx
+++ b/sampleprojects/Scopa/excel/Scopa.xlsx
@@ -300,7 +300,7 @@
     <t>TABLE_NUMBER: 4080</t>
   </si>
   <si>
-    <t>there is card in player.pile where (card.rank == 7 and card.suit == 0)</t>
+    <t>there is card in player.pile where card.rank == 7 and card.suit == 0</t>
   </si>
   <si>
     <t>set player.has_settebello = true;</t>

--- a/sampleprojects/Scopa/excel/Scopa.xlsx
+++ b/sampleprojects/Scopa/excel/Scopa.xlsx
@@ -13,16 +13,15 @@
     <sheet name="Score Scopa" sheetId="5" r:id="rId8"/>
     <sheet name="Primiera Value" sheetId="6" r:id="rId9"/>
     <sheet name="Suit Best" sheetId="7" r:id="rId10"/>
-    <sheet name="Suit Best Inner" sheetId="8" r:id="rId11"/>
-    <sheet name="Score Primiera" sheetId="9" r:id="rId12"/>
-    <sheet name="Score Settebello" sheetId="10" r:id="rId13"/>
+    <sheet name="Score Primiera" sheetId="8" r:id="rId11"/>
+    <sheet name="Score Settebello" sheetId="9" r:id="rId12"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>DT: Resolve Capture</t>
   </si>
@@ -249,25 +248,7 @@
     <t>for all player.suit_groups</t>
   </si>
   <si>
-    <t>perform Suit_Best_Inner</t>
-  </si>
-  <si>
-    <t>DT: Suit Best Inner</t>
-  </si>
-  <si>
-    <t>TABLE_NUMBER: 4060</t>
-  </si>
-  <si>
-    <t>for all grp.members</t>
-  </si>
-  <si>
-    <t>a better card for this suit</t>
-  </si>
-  <si>
-    <t>card.primiera &gt; grp.best</t>
-  </si>
-  <si>
-    <t>set grp.best = card.primiera;</t>
+    <t>set grp.best = max of primiera in grp.members;</t>
   </si>
   <si>
     <t>DT: Score Primiera</t>
@@ -666,522 +647,6 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="20"/>
-    <col customWidth="true" max="3" min="2" width="40"/>
-    <col customWidth="true" max="19" min="4" width="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4</v>
-      </c>
-      <c r="H10" s="1">
-        <v>5</v>
-      </c>
-      <c r="I10" s="1">
-        <v>6</v>
-      </c>
-      <c r="J10" s="1">
-        <v>7</v>
-      </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
-        <v>9</v>
-      </c>
-      <c r="M10" s="1">
-        <v>10</v>
-      </c>
-      <c r="N10" s="1">
-        <v>11</v>
-      </c>
-      <c r="O10" s="1">
-        <v>12</v>
-      </c>
-      <c r="P10" s="1">
-        <v>13</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>14</v>
-      </c>
-      <c r="R10" s="1">
-        <v>15</v>
-      </c>
-      <c r="S10" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>2</v>
-      </c>
-      <c r="F13" s="4">
-        <v>3</v>
-      </c>
-      <c r="G13" s="4">
-        <v>4</v>
-      </c>
-      <c r="H13" s="4">
-        <v>5</v>
-      </c>
-      <c r="I13" s="4">
-        <v>6</v>
-      </c>
-      <c r="J13" s="4">
-        <v>7</v>
-      </c>
-      <c r="K13" s="4">
-        <v>8</v>
-      </c>
-      <c r="L13" s="4">
-        <v>9</v>
-      </c>
-      <c r="M13" s="4">
-        <v>10</v>
-      </c>
-      <c r="N13" s="4">
-        <v>11</v>
-      </c>
-      <c r="O13" s="4">
-        <v>12</v>
-      </c>
-      <c r="P13" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>14</v>
-      </c>
-      <c r="R13" s="4">
-        <v>15</v>
-      </c>
-      <c r="S13" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5">
-        <v>1</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
-      </c>
-      <c r="F16" s="1">
-        <v>3</v>
-      </c>
-      <c r="G16" s="1">
-        <v>4</v>
-      </c>
-      <c r="H16" s="1">
-        <v>5</v>
-      </c>
-      <c r="I16" s="1">
-        <v>6</v>
-      </c>
-      <c r="J16" s="1">
-        <v>7</v>
-      </c>
-      <c r="K16" s="1">
-        <v>8</v>
-      </c>
-      <c r="L16" s="1">
-        <v>9</v>
-      </c>
-      <c r="M16" s="1">
-        <v>10</v>
-      </c>
-      <c r="N16" s="1">
-        <v>11</v>
-      </c>
-      <c r="O16" s="1">
-        <v>12</v>
-      </c>
-      <c r="P16" s="1">
-        <v>13</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>14</v>
-      </c>
-      <c r="R16" s="1">
-        <v>15</v>
-      </c>
-      <c r="S16" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5">
-        <v>1</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A4:S4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
-  </mergeCells>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -5342,303 +4807,508 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7">
-      <c r="A7" s="5">
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4</v>
+      </c>
+      <c r="H12" s="1">
+        <v>5</v>
+      </c>
+      <c r="I12" s="1">
         <v>6</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1" t="s">
+      <c r="J12" s="1">
         <v>7</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="K12" s="1">
+        <v>8</v>
+      </c>
+      <c r="L12" s="1">
+        <v>9</v>
+      </c>
+      <c r="M12" s="1">
+        <v>10</v>
+      </c>
+      <c r="N12" s="1">
         <v>11</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
+      <c r="O12" s="1">
         <v>12</v>
       </c>
-      <c r="D11" s="1">
+      <c r="P12" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>14</v>
+      </c>
+      <c r="R12" s="1">
+        <v>15</v>
+      </c>
+      <c r="S12" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F15" s="4">
         <v>3</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G15" s="4">
         <v>4</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H15" s="4">
         <v>5</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I15" s="4">
         <v>6</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J15" s="4">
         <v>7</v>
       </c>
-      <c r="K11" s="1">
-        <v>8</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
         <v>9</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M15" s="4">
         <v>10</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N15" s="4">
         <v>11</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O15" s="4">
         <v>12</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P15" s="4">
         <v>13</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q15" s="4">
         <v>14</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R15" s="4">
         <v>15</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S15" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5">
+    <row r="16">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
+      <c r="B17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
         <v>3</v>
       </c>
-      <c r="G14" s="4">
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
         <v>4</v>
       </c>
-      <c r="H14" s="4">
-        <v>5</v>
-      </c>
-      <c r="I14" s="4">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4">
-        <v>7</v>
-      </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
-        <v>9</v>
-      </c>
-      <c r="M14" s="4">
-        <v>10</v>
-      </c>
-      <c r="N14" s="4">
-        <v>11</v>
-      </c>
-      <c r="O14" s="4">
-        <v>12</v>
-      </c>
-      <c r="P14" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>14</v>
-      </c>
-      <c r="R14" s="4">
-        <v>15</v>
-      </c>
-      <c r="S14" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="2" t="s">
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="C7:S7"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
     <mergeCell ref="C9:S9"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C10:S10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -5654,7 +5324,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5723,7 +5393,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5794,304 +5464,307 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9">
-      <c r="A9" s="5">
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5">
+      <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
+      <c r="O10" s="1">
         <v>12</v>
       </c>
-      <c r="D12" s="1">
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
         <v>1</v>
       </c>
-      <c r="E12" s="1">
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F13" s="4">
         <v>3</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H13" s="4">
         <v>5</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I13" s="4">
         <v>6</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J13" s="4">
         <v>7</v>
       </c>
-      <c r="K12" s="1">
-        <v>8</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="K13" s="4">
+        <v>8</v>
+      </c>
+      <c r="L13" s="4">
         <v>9</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M13" s="4">
         <v>10</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N13" s="4">
         <v>11</v>
       </c>
-      <c r="O12" s="1">
+      <c r="O13" s="4">
         <v>12</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P13" s="4">
         <v>13</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q13" s="4">
         <v>14</v>
       </c>
-      <c r="R12" s="1">
+      <c r="R13" s="4">
         <v>15</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S13" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5">
+    <row r="14">
+      <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5</v>
+      </c>
+      <c r="I16" s="1">
+        <v>6</v>
+      </c>
+      <c r="J16" s="1">
+        <v>7</v>
+      </c>
+      <c r="K16" s="1">
+        <v>8</v>
+      </c>
+      <c r="L16" s="1">
+        <v>9</v>
+      </c>
+      <c r="M16" s="1">
+        <v>10</v>
+      </c>
+      <c r="N16" s="1">
+        <v>11</v>
+      </c>
+      <c r="O16" s="1">
+        <v>12</v>
+      </c>
+      <c r="P16" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="1">
         <v>14</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="R16" s="1">
         <v>15</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="S16" s="1">
         <v>16</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4">
-        <v>2</v>
-      </c>
-      <c r="F15" s="4">
-        <v>3</v>
-      </c>
-      <c r="G15" s="4">
-        <v>4</v>
-      </c>
-      <c r="H15" s="4">
-        <v>5</v>
-      </c>
-      <c r="I15" s="4">
-        <v>6</v>
-      </c>
-      <c r="J15" s="4">
-        <v>7</v>
-      </c>
-      <c r="K15" s="4">
-        <v>8</v>
-      </c>
-      <c r="L15" s="4">
-        <v>9</v>
-      </c>
-      <c r="M15" s="4">
-        <v>10</v>
-      </c>
-      <c r="N15" s="4">
-        <v>11</v>
-      </c>
-      <c r="O15" s="4">
-        <v>12</v>
-      </c>
-      <c r="P15" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>14</v>
-      </c>
-      <c r="R15" s="4">
-        <v>15</v>
-      </c>
-      <c r="S15" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>8</v>
@@ -6139,126 +5812,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5">
-        <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5">
-        <v>4</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
@@ -6267,10 +5822,9 @@
     <mergeCell ref="C6:S6"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:S8"/>
-    <mergeCell ref="C9:S9"/>
-    <mergeCell ref="C10:S10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/sampleprojects/Scopa/excel/Scopa.xlsx
+++ b/sampleprojects/Scopa/excel/Scopa.xlsx
@@ -50,7 +50,7 @@
     <t/>
   </si>
   <si>
-    <t>set move.capture_found = 0; set move.capture_size = 0; set move.is_scopa = false;</t>
+    <t>set move.capture_found = 0; set move.capture_size = 0; set move.is_scopa = false; for all move.table_cards set card.value = card.rank;</t>
   </si>
   <si>
     <t>subsets(move.table_cards, "combo", "value", move.options)</t>
